--- a/JsonConverter/ExcelFiles/Equpment.xlsx
+++ b/JsonConverter/ExcelFiles/Equpment.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="19410" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -21,58 +21,67 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>동 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은 갑옷</x:t>
+  </x:si>
+  <x:si>
     <x:t>Epic</x:t>
   </x:si>
   <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금 갑옷</x:t>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>Rare</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>IconPath</x:t>
@@ -81,25 +90,16 @@
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Armor_2</x:t>
   </x:si>
   <x:si>
+    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_1</x:t>
   </x:si>
   <x:si>
     <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
@@ -907,82 +907,83 @@
     <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
     <x:col min="5" max="5" width="30.5703125" style="2" customWidth="1"/>
+    <x:col min="8" max="8" width="24.4296875" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="15" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="16" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="16" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="16">
         <x:v>10</x:v>
@@ -991,7 +992,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H4" s="16" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
@@ -1003,19 +1004,19 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="17" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="16" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E5" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="16">
         <x:v>10</x:v>
@@ -1036,19 +1037,19 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="18" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="18" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="18" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="16" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="16">
         <x:v>10</x:v>
@@ -1057,7 +1058,7 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="H6" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -2292,7 +2293,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Equpment.xlsx
+++ b/JsonConverter/ExcelFiles/Equpment.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20925" windowHeight="11340"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -19,90 +19,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_2]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_3</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Armor_1</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rare</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_2</x:t>
+    <x:t>DefBonus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DexBonus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LukBonus</x:t>
   </x:si>
   <x:si>
     <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -238,7 +247,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="20">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -903,429 +915,466 @@
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="30.5703125" style="2" customWidth="1"/>
-    <x:col min="8" max="8" width="24.4296875" customWidth="1"/>
+    <x:col min="1" max="1" width="23" style="3" customWidth="1"/>
+    <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
+    <x:col min="3" max="3" width="50.7109375" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="7.0859375" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="30.5703125" style="1" customWidth="1"/>
+    <x:col min="9" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A1" s="3" t="s">
+      <x:c r="A1" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+    </x:row>
+    <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A2" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A3" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H3" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A2" s="3" t="s">
+      <x:c r="I3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E4" s="17" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F4" s="17">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G4" s="17">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="6">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J4" s="6">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K4" s="6">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
+      <x:c r="O4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A5" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E5" s="17" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F5" s="17">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G5" s="17">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H5" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I5" s="6">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J5" s="6">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A3" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
+      <x:c r="K5" s="6">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L5" s="6"/>
+      <x:c r="M5" s="6"/>
+      <x:c r="N5" s="6"/>
+      <x:c r="O5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A6" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B6" s="19" t="s">
         <x:v>21</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="15" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="15" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E4" s="16" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F4" s="16">
+      <x:c r="C6" s="19" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G4" s="16">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="L4" s="5"/>
-      <x:c r="M4" s="5"/>
-      <x:c r="N4" s="5"/>
-      <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="17" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="17" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F5" s="16">
+      <x:c r="F6" s="17">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G5" s="16">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="18" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D6" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F6" s="16">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G6" s="16">
+      <x:c r="G6" s="17">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5"/>
-      <x:c r="L6" s="5"/>
-      <x:c r="M6" s="5"/>
-      <x:c r="N6" s="5"/>
-      <x:c r="O6" s="5"/>
+      <x:c r="H6" s="17" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I6" s="6">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J6" s="6">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K6" s="6">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L6" s="6"/>
+      <x:c r="M6" s="6"/>
+      <x:c r="N6" s="6"/>
+      <x:c r="O6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="14"/>
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="14"/>
-      <x:c r="D7" s="13"/>
-      <x:c r="E7" s="13"/>
-      <x:c r="F7" s="13"/>
-      <x:c r="G7" s="13"/>
-      <x:c r="H7" s="13"/>
-      <x:c r="I7" s="5"/>
-      <x:c r="J7" s="5"/>
-      <x:c r="K7" s="5"/>
-      <x:c r="L7" s="5"/>
-      <x:c r="M7" s="5"/>
-      <x:c r="N7" s="5"/>
-      <x:c r="O7" s="5"/>
+      <x:c r="A7" s="15"/>
+      <x:c r="B7" s="15"/>
+      <x:c r="C7" s="15"/>
+      <x:c r="D7" s="14"/>
+      <x:c r="E7" s="14"/>
+      <x:c r="F7" s="14"/>
+      <x:c r="G7" s="14"/>
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="6"/>
+      <x:c r="J7" s="6"/>
+      <x:c r="K7" s="6"/>
+      <x:c r="L7" s="6"/>
+      <x:c r="M7" s="6"/>
+      <x:c r="N7" s="6"/>
+      <x:c r="O7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="14"/>
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="14"/>
-      <x:c r="D8" s="13"/>
-      <x:c r="E8" s="13"/>
-      <x:c r="F8" s="13"/>
-      <x:c r="G8" s="13"/>
-      <x:c r="H8" s="13"/>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="5"/>
-      <x:c r="N8" s="5"/>
-      <x:c r="O8" s="5"/>
+      <x:c r="A8" s="15"/>
+      <x:c r="B8" s="15"/>
+      <x:c r="C8" s="15"/>
+      <x:c r="D8" s="14"/>
+      <x:c r="E8" s="14"/>
+      <x:c r="F8" s="14"/>
+      <x:c r="G8" s="14"/>
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="6"/>
+      <x:c r="J8" s="6"/>
+      <x:c r="K8" s="6"/>
+      <x:c r="L8" s="6"/>
+      <x:c r="M8" s="6"/>
+      <x:c r="N8" s="6"/>
+      <x:c r="O8" s="6"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="14"/>
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="14"/>
-      <x:c r="D9" s="13"/>
-      <x:c r="E9" s="13"/>
-      <x:c r="F9" s="13"/>
-      <x:c r="G9" s="13"/>
-      <x:c r="H9" s="13"/>
-      <x:c r="I9" s="5"/>
-      <x:c r="J9" s="5"/>
-      <x:c r="K9" s="5"/>
-      <x:c r="L9" s="5"/>
-      <x:c r="M9" s="5"/>
-      <x:c r="N9" s="5"/>
-      <x:c r="O9" s="5"/>
+      <x:c r="A9" s="15"/>
+      <x:c r="B9" s="15"/>
+      <x:c r="C9" s="15"/>
+      <x:c r="D9" s="14"/>
+      <x:c r="E9" s="14"/>
+      <x:c r="F9" s="14"/>
+      <x:c r="G9" s="14"/>
+      <x:c r="H9" s="14"/>
+      <x:c r="I9" s="6"/>
+      <x:c r="J9" s="6"/>
+      <x:c r="K9" s="6"/>
+      <x:c r="L9" s="6"/>
+      <x:c r="M9" s="6"/>
+      <x:c r="N9" s="6"/>
+      <x:c r="O9" s="6"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="8"/>
-      <x:c r="B10" s="8"/>
-      <x:c r="C10" s="8"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
-      <x:c r="J10" s="5"/>
-      <x:c r="K10" s="5"/>
-      <x:c r="L10" s="5"/>
-      <x:c r="M10" s="5"/>
-      <x:c r="N10" s="5"/>
-      <x:c r="O10" s="5"/>
+      <x:c r="A10" s="9"/>
+      <x:c r="B10" s="9"/>
+      <x:c r="C10" s="9"/>
+      <x:c r="D10" s="6"/>
+      <x:c r="E10" s="6"/>
+      <x:c r="F10" s="6"/>
+      <x:c r="G10" s="6"/>
+      <x:c r="H10" s="6"/>
+      <x:c r="I10" s="6"/>
+      <x:c r="J10" s="6"/>
+      <x:c r="K10" s="6"/>
+      <x:c r="L10" s="6"/>
+      <x:c r="M10" s="6"/>
+      <x:c r="N10" s="6"/>
+      <x:c r="O10" s="6"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="8"/>
-      <x:c r="B11" s="8"/>
-      <x:c r="C11" s="8"/>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5"/>
-      <x:c r="H11" s="5"/>
-      <x:c r="I11" s="5"/>
-      <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-      <x:c r="L11" s="5"/>
-      <x:c r="M11" s="5"/>
-      <x:c r="N11" s="5"/>
-      <x:c r="O11" s="5"/>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="9"/>
+      <x:c r="C11" s="9"/>
+      <x:c r="D11" s="6"/>
+      <x:c r="E11" s="6"/>
+      <x:c r="F11" s="6"/>
+      <x:c r="G11" s="6"/>
+      <x:c r="H11" s="6"/>
+      <x:c r="I11" s="6"/>
+      <x:c r="J11" s="6"/>
+      <x:c r="K11" s="6"/>
+      <x:c r="L11" s="6"/>
+      <x:c r="M11" s="6"/>
+      <x:c r="N11" s="6"/>
+      <x:c r="O11" s="6"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5"/>
-      <x:c r="H12" s="5"/>
-      <x:c r="I12" s="5"/>
-      <x:c r="J12" s="5"/>
-      <x:c r="K12" s="5"/>
-      <x:c r="L12" s="5"/>
-      <x:c r="M12" s="5"/>
-      <x:c r="N12" s="5"/>
-      <x:c r="O12" s="5"/>
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="8"/>
+      <x:c r="C12" s="8"/>
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6"/>
+      <x:c r="F12" s="6"/>
+      <x:c r="G12" s="6"/>
+      <x:c r="H12" s="6"/>
+      <x:c r="I12" s="6"/>
+      <x:c r="J12" s="6"/>
+      <x:c r="K12" s="6"/>
+      <x:c r="L12" s="6"/>
+      <x:c r="M12" s="6"/>
+      <x:c r="N12" s="6"/>
+      <x:c r="O12" s="6"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6"/>
-      <x:c r="B13" s="6"/>
-      <x:c r="C13" s="6"/>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
-      <x:c r="I13" s="5"/>
-      <x:c r="J13" s="5"/>
-      <x:c r="K13" s="5"/>
-      <x:c r="L13" s="5"/>
-      <x:c r="M13" s="5"/>
-      <x:c r="N13" s="5"/>
-      <x:c r="O13" s="5"/>
+      <x:c r="A13" s="7"/>
+      <x:c r="B13" s="7"/>
+      <x:c r="C13" s="7"/>
+      <x:c r="D13" s="6"/>
+      <x:c r="E13" s="6"/>
+      <x:c r="F13" s="6"/>
+      <x:c r="G13" s="6"/>
+      <x:c r="H13" s="6"/>
+      <x:c r="I13" s="6"/>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="6"/>
+      <x:c r="L13" s="6"/>
+      <x:c r="M13" s="6"/>
+      <x:c r="N13" s="6"/>
+      <x:c r="O13" s="6"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="8"/>
-      <x:c r="B14" s="8"/>
-      <x:c r="C14" s="8"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
-      <x:c r="H14" s="5"/>
-      <x:c r="I14" s="5"/>
-      <x:c r="J14" s="5"/>
-      <x:c r="K14" s="5"/>
-      <x:c r="L14" s="5"/>
-      <x:c r="M14" s="5"/>
-      <x:c r="N14" s="5"/>
-      <x:c r="O14" s="5"/>
+      <x:c r="A14" s="9"/>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
+      <x:c r="D14" s="6"/>
+      <x:c r="E14" s="6"/>
+      <x:c r="F14" s="6"/>
+      <x:c r="G14" s="6"/>
+      <x:c r="H14" s="6"/>
+      <x:c r="I14" s="6"/>
+      <x:c r="J14" s="6"/>
+      <x:c r="K14" s="6"/>
+      <x:c r="L14" s="6"/>
+      <x:c r="M14" s="6"/>
+      <x:c r="N14" s="6"/>
+      <x:c r="O14" s="6"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="8"/>
-      <x:c r="B15" s="8"/>
-      <x:c r="C15" s="8"/>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="5"/>
-      <x:c r="H15" s="5"/>
-      <x:c r="I15" s="5"/>
-      <x:c r="J15" s="5"/>
-      <x:c r="K15" s="5"/>
-      <x:c r="L15" s="5"/>
-      <x:c r="M15" s="5"/>
-      <x:c r="N15" s="5"/>
-      <x:c r="O15" s="5"/>
+      <x:c r="A15" s="9"/>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="9"/>
+      <x:c r="D15" s="6"/>
+      <x:c r="E15" s="6"/>
+      <x:c r="F15" s="6"/>
+      <x:c r="G15" s="6"/>
+      <x:c r="H15" s="6"/>
+      <x:c r="I15" s="6"/>
+      <x:c r="J15" s="6"/>
+      <x:c r="K15" s="6"/>
+      <x:c r="L15" s="6"/>
+      <x:c r="M15" s="6"/>
+      <x:c r="N15" s="6"/>
+      <x:c r="O15" s="6"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="9"/>
-      <x:c r="B16" s="9"/>
-      <x:c r="C16" s="9"/>
+      <x:c r="A16" s="10"/>
+      <x:c r="B16" s="10"/>
+      <x:c r="C16" s="10"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="10"/>
-      <x:c r="B17" s="10"/>
-      <x:c r="C17" s="10"/>
+      <x:c r="A17" s="11"/>
+      <x:c r="B17" s="11"/>
+      <x:c r="C17" s="11"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="10"/>
-      <x:c r="B18" s="10"/>
-      <x:c r="C18" s="10"/>
+      <x:c r="A18" s="11"/>
+      <x:c r="B18" s="11"/>
+      <x:c r="C18" s="11"/>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="10"/>
-      <x:c r="B19" s="10"/>
-      <x:c r="C19" s="10"/>
-      <x:c r="D19" s="5"/>
-      <x:c r="E19" s="5"/>
+      <x:c r="A19" s="11"/>
+      <x:c r="B19" s="11"/>
+      <x:c r="C19" s="11"/>
+      <x:c r="D19" s="6"/>
+      <x:c r="E19" s="6"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="10"/>
-      <x:c r="B20" s="10"/>
-      <x:c r="C20" s="10"/>
+      <x:c r="A20" s="11"/>
+      <x:c r="B20" s="11"/>
+      <x:c r="C20" s="11"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="10"/>
-      <x:c r="B21" s="10"/>
-      <x:c r="C21" s="10"/>
+      <x:c r="A21" s="11"/>
+      <x:c r="B21" s="11"/>
+      <x:c r="C21" s="11"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="10"/>
-      <x:c r="B22" s="10"/>
-      <x:c r="C22" s="10"/>
+      <x:c r="A22" s="11"/>
+      <x:c r="B22" s="11"/>
+      <x:c r="C22" s="11"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="10"/>
-      <x:c r="B23" s="10"/>
-      <x:c r="C23" s="10"/>
+      <x:c r="A23" s="11"/>
+      <x:c r="B23" s="11"/>
+      <x:c r="C23" s="11"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="10"/>
-      <x:c r="B24" s="10"/>
-      <x:c r="C24" s="10"/>
+      <x:c r="A24" s="11"/>
+      <x:c r="B24" s="11"/>
+      <x:c r="C24" s="11"/>
     </x:row>
     <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="10"/>
-      <x:c r="B25" s="10"/>
-      <x:c r="C25" s="10"/>
-      <x:c r="E25" s="5"/>
+      <x:c r="A25" s="11"/>
+      <x:c r="B25" s="11"/>
+      <x:c r="C25" s="11"/>
+      <x:c r="E25" s="6"/>
     </x:row>
     <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="11"/>
-      <x:c r="E26" s="5"/>
+      <x:c r="A26" s="12"/>
+      <x:c r="B26" s="12"/>
+      <x:c r="C26" s="12"/>
+      <x:c r="E26" s="6"/>
     </x:row>
     <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="11"/>
-      <x:c r="E27" s="5"/>
+      <x:c r="A27" s="12"/>
+      <x:c r="B27" s="12"/>
+      <x:c r="C27" s="12"/>
+      <x:c r="E27" s="6"/>
     </x:row>
     <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="11"/>
-      <x:c r="E28" s="5"/>
+      <x:c r="A28" s="12"/>
+      <x:c r="B28" s="12"/>
+      <x:c r="C28" s="12"/>
+      <x:c r="E28" s="6"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
+      <x:c r="A29" s="12"/>
+      <x:c r="B29" s="12"/>
+      <x:c r="C29" s="12"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
+      <x:c r="A30" s="12"/>
+      <x:c r="B30" s="12"/>
+      <x:c r="C30" s="12"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
+      <x:c r="A31" s="12"/>
+      <x:c r="B31" s="12"/>
+      <x:c r="C31" s="12"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="12"/>
-      <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
+      <x:c r="A32" s="13"/>
+      <x:c r="B32" s="13"/>
+      <x:c r="C32" s="13"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="12"/>
-      <x:c r="B33" s="12"/>
-      <x:c r="C33" s="12"/>
+      <x:c r="A33" s="13"/>
+      <x:c r="B33" s="13"/>
+      <x:c r="C33" s="13"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="12"/>
-      <x:c r="B34" s="12"/>
-      <x:c r="C34" s="12"/>
+      <x:c r="A34" s="13"/>
+      <x:c r="B34" s="13"/>
+      <x:c r="C34" s="13"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="12"/>
-      <x:c r="B35" s="12"/>
-      <x:c r="C35" s="12"/>
+      <x:c r="A35" s="13"/>
+      <x:c r="B35" s="13"/>
+      <x:c r="C35" s="13"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
